--- a/pcb/robot/usb-pd-module/USB_PD_Module_BOM_B-E101367AA1.xlsx
+++ b/pcb/robot/usb-pd-module/USB_PD_Module_BOM_B-E101367AA1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JHORDAN\FREELANCE\PROYECTOS\KICAD_USB_PD_MODULAR\Github\smartphone-robot-cad\pcb\robot\usb-pd-module\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2340D6-4C71-42E5-8910-94E549246CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4332A5-F926-4042-8410-491D180DC1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -828,6 +828,15 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -849,15 +858,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,6 +873,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1905000</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>122465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>470398</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>199074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20C780C9-F0D2-44A6-9FD2-DE2F1847B2CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3796393" y="6340929"/>
+          <a:ext cx="6811326" cy="2934109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1196,87 +1245,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
       <c r="J1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
       <c r="O1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
     </row>
     <row r="2" spans="1:20" ht="27.75" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
       <c r="J2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
       <c r="O2" s="5"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
     </row>
     <row r="3" spans="1:20" ht="22.5" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21" t="s">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="22"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="25"/>
     </row>
     <row r="4" spans="1:20" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -1640,65 +1689,65 @@
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="28" customFormat="1" ht="14.25">
-      <c r="A10" s="26">
+    <row r="10" spans="1:20" s="21" customFormat="1" ht="14.25">
+      <c r="A10" s="19">
         <v>6</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="20">
         <v>1</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="26">
+      <c r="H10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="19">
         <v>2188470001</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="26" t="s">
+      <c r="L10" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="19">
         <v>5</v>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="19">
         <v>1</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="19">
         <v>6</v>
       </c>
-      <c r="P10" s="26">
+      <c r="P10" s="19">
         <v>1.2937700000000001</v>
       </c>
-      <c r="Q10" s="26">
+      <c r="Q10" s="19">
         <v>7.76</v>
       </c>
-      <c r="R10" s="26" t="s">
+      <c r="R10" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="S10" s="26" t="s">
+      <c r="S10" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="T10" s="26" t="s">
+      <c r="T10" s="19" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2974,5 +3023,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>